--- a/cursos/tu_turno/moodle/herramientas/Herramientas_TTDF.xlsx
+++ b/cursos/tu_turno/moodle/herramientas/Herramientas_TTDF.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Deudas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Fondo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Meta" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Quincena" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1127,4 +1128,107 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Mi quincena con turnos extra</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Escribe solo en las celdas rosas. Usa montos inventados o aproximados; este archivo es tuyo y no se comparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sueldo base de la quincena</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Turnos extra</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pago por turno extra</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Descuentos (adelantos, préstamos, FONACOT)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lo que me llega</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
+        <f>B4+B5*B6-B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ahorro, apartado primero (10%)</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
+        <f>ROUND(B8*0.1,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Para gastar la quincena</t>
+        </is>
+      </c>
+      <c r="B10" s="8">
+        <f>B8-B9</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>